--- a/Application/Filtering_all.xlsx
+++ b/Application/Filtering_all.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mirka\PycharmProjects\PythonProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7FF636F-F0B1-44E6-9982-316A45FF8765}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CBDE7D9-22E1-4C35-90C9-F45726A383C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="717" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="717" uniqueCount="161">
   <si>
     <t>Method</t>
   </si>
@@ -62,9 +62,6 @@
     <t>Classification, Regression</t>
   </si>
   <si>
-    <t>Local,Global</t>
-  </si>
-  <si>
     <t>Shapley values</t>
   </si>
   <si>
@@ -167,9 +164,6 @@
     <t>CEM</t>
   </si>
   <si>
-    <t>IMG,TAB,TXT,GRH,TS,VID</t>
-  </si>
-  <si>
     <t>Guided Proto</t>
   </si>
   <si>
@@ -311,9 +305,6 @@
     <t>Shapley Flow</t>
   </si>
   <si>
-    <t>L, G</t>
-  </si>
-  <si>
     <t>FBT</t>
   </si>
   <si>
@@ -525,6 +516,12 @@
   </si>
   <si>
     <t>Input data type</t>
+  </si>
+  <si>
+    <t>Local, Global</t>
+  </si>
+  <si>
+    <t>IMG, TAB, TXT, GRH, TS, VID</t>
   </si>
 </sst>
 </file>
@@ -859,25 +856,25 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D1" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1" t="s">
+        <v>135</v>
+      </c>
+      <c r="F1" t="s">
         <v>133</v>
       </c>
-      <c r="C1" t="s">
-        <v>135</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="G1" t="s">
+        <v>158</v>
+      </c>
+      <c r="H1" t="s">
         <v>134</v>
-      </c>
-      <c r="E1" t="s">
-        <v>138</v>
-      </c>
-      <c r="F1" t="s">
-        <v>136</v>
-      </c>
-      <c r="G1" t="s">
-        <v>161</v>
-      </c>
-      <c r="H1" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -900,7 +897,7 @@
         <v>5</v>
       </c>
       <c r="H2" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -911,7 +908,7 @@
         <v>2017</v>
       </c>
       <c r="C3" t="s">
-        <v>7</v>
+        <v>159</v>
       </c>
       <c r="D3" t="s">
         <v>3</v>
@@ -923,12 +920,12 @@
         <v>5</v>
       </c>
       <c r="H3" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B4">
         <v>2014</v>
@@ -943,15 +940,15 @@
         <v>6</v>
       </c>
       <c r="G4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H4" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>2015</v>
@@ -960,24 +957,24 @@
         <v>4</v>
       </c>
       <c r="D5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" t="s">
+        <v>137</v>
+      </c>
+      <c r="F5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" t="s">
         <v>11</v>
       </c>
-      <c r="E5" t="s">
-        <v>140</v>
-      </c>
-      <c r="F5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5" t="s">
-        <v>12</v>
-      </c>
       <c r="H5" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B6">
         <v>2013</v>
@@ -986,24 +983,24 @@
         <v>4</v>
       </c>
       <c r="D6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" t="s">
+        <v>137</v>
+      </c>
+      <c r="F6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" t="s">
         <v>11</v>
       </c>
-      <c r="E6" t="s">
-        <v>140</v>
-      </c>
-      <c r="F6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6" t="s">
-        <v>12</v>
-      </c>
       <c r="H6" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B7">
         <v>2019</v>
@@ -1012,24 +1009,24 @@
         <v>4</v>
       </c>
       <c r="D7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E7" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="F7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H7" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B8">
         <v>2017</v>
@@ -1038,24 +1035,24 @@
         <v>4</v>
       </c>
       <c r="D8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" t="s">
+        <v>137</v>
+      </c>
+      <c r="F8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" t="s">
         <v>11</v>
       </c>
-      <c r="E8" t="s">
-        <v>140</v>
-      </c>
-      <c r="F8" t="s">
-        <v>13</v>
-      </c>
-      <c r="G8" t="s">
-        <v>12</v>
-      </c>
       <c r="H8" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B9">
         <v>2018</v>
@@ -1067,18 +1064,18 @@
         <v>3</v>
       </c>
       <c r="F9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H9" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B10">
         <v>2017</v>
@@ -1087,24 +1084,24 @@
         <v>4</v>
       </c>
       <c r="D10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" t="s">
+        <v>137</v>
+      </c>
+      <c r="F10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" t="s">
         <v>11</v>
       </c>
-      <c r="E10" t="s">
-        <v>140</v>
-      </c>
-      <c r="F10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G10" t="s">
-        <v>12</v>
-      </c>
       <c r="H10" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B11">
         <v>2017</v>
@@ -1116,47 +1113,47 @@
         <v>3</v>
       </c>
       <c r="F11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H11" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B12">
         <v>2017</v>
       </c>
       <c r="C12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D12" t="s">
         <v>3</v>
       </c>
       <c r="F12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H12" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B13">
         <v>2015</v>
       </c>
       <c r="C13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D13" t="s">
         <v>3</v>
@@ -1165,15 +1162,15 @@
         <v>6</v>
       </c>
       <c r="G13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H13" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B14">
         <v>2017</v>
@@ -1182,24 +1179,24 @@
         <v>4</v>
       </c>
       <c r="D14" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E14" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H14" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B15">
         <v>2013</v>
@@ -1208,24 +1205,24 @@
         <v>4</v>
       </c>
       <c r="D15" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E15" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="F15" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H15" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B16">
         <v>2017</v>
@@ -1234,30 +1231,30 @@
         <v>4</v>
       </c>
       <c r="D16" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E16" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F16" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G16" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H16" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B17">
         <v>2001</v>
       </c>
       <c r="C17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D17" t="s">
         <v>3</v>
@@ -1266,15 +1263,15 @@
         <v>6</v>
       </c>
       <c r="G17" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H17" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B18">
         <v>2017</v>
@@ -1283,24 +1280,24 @@
         <v>4</v>
       </c>
       <c r="D18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E18" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F18" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H18" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B19">
         <v>2014</v>
@@ -1309,24 +1306,24 @@
         <v>4</v>
       </c>
       <c r="D19" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E19" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F19" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H19" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B20">
         <v>2017</v>
@@ -1335,24 +1332,24 @@
         <v>4</v>
       </c>
       <c r="D20" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E20" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F20" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G20" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H20" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B21">
         <v>2017</v>
@@ -1361,24 +1358,24 @@
         <v>4</v>
       </c>
       <c r="D21" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E21" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F21" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G21" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H21" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B22">
         <v>2015</v>
@@ -1387,24 +1384,24 @@
         <v>4</v>
       </c>
       <c r="D22" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E22" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="F22" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G22" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H22" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B23">
         <v>2010</v>
@@ -1413,24 +1410,24 @@
         <v>4</v>
       </c>
       <c r="D23" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E23" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F23" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G23" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H23" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B24">
         <v>2015</v>
@@ -1439,24 +1436,24 @@
         <v>4</v>
       </c>
       <c r="D24" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E24" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="F24" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G24" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H24" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B25">
         <v>2016</v>
@@ -1465,24 +1462,24 @@
         <v>4</v>
       </c>
       <c r="D25" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E25" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F25" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G25" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H25" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B26">
         <v>2018</v>
@@ -1494,18 +1491,18 @@
         <v>3</v>
       </c>
       <c r="F26" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G26" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H26" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B27">
         <v>2017</v>
@@ -1514,21 +1511,21 @@
         <v>4</v>
       </c>
       <c r="D27" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F27" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G27" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H27" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B28">
         <v>2018</v>
@@ -1537,21 +1534,21 @@
         <v>4</v>
       </c>
       <c r="D28" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F28" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G28" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H28" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B29">
         <v>2018</v>
@@ -1560,21 +1557,21 @@
         <v>4</v>
       </c>
       <c r="D29" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F29" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G29" t="s">
-        <v>42</v>
+        <v>160</v>
       </c>
       <c r="H29" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B30">
         <v>2019</v>
@@ -1586,18 +1583,18 @@
         <v>3</v>
       </c>
       <c r="F30" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G30" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H30" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B31">
         <v>2020</v>
@@ -1609,93 +1606,93 @@
         <v>3</v>
       </c>
       <c r="F31" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G31" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H31" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B32">
         <v>2019</v>
       </c>
       <c r="C32" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D32" t="s">
         <v>3</v>
       </c>
       <c r="F32" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G32" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H32" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B33">
         <v>2020</v>
       </c>
       <c r="C33" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D33" t="s">
         <v>3</v>
       </c>
       <c r="F33" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G33" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H33" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B34">
         <v>2017</v>
       </c>
       <c r="C34" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D34" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F34" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G34" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H34" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B35">
         <v>2016</v>
       </c>
       <c r="C35" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D35" t="s">
         <v>3</v>
@@ -1704,21 +1701,21 @@
         <v>6</v>
       </c>
       <c r="G35" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H35" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B36">
         <v>1995</v>
       </c>
       <c r="C36" t="s">
-        <v>7</v>
+        <v>159</v>
       </c>
       <c r="D36" t="s">
         <v>3</v>
@@ -1727,15 +1724,15 @@
         <v>6</v>
       </c>
       <c r="G36" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H36" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B37">
         <v>2015</v>
@@ -1744,27 +1741,27 @@
         <v>4</v>
       </c>
       <c r="D37" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F37" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G37" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H37" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B38">
         <v>2016</v>
       </c>
       <c r="C38" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D38" t="s">
         <v>3</v>
@@ -1773,15 +1770,15 @@
         <v>6</v>
       </c>
       <c r="G38" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H38" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B39">
         <v>2018</v>
@@ -1790,24 +1787,24 @@
         <v>4</v>
       </c>
       <c r="D39" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E39" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F39" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G39" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H39" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B40">
         <v>2019</v>
@@ -1819,18 +1816,18 @@
         <v>3</v>
       </c>
       <c r="F40" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G40" t="s">
-        <v>42</v>
+        <v>160</v>
       </c>
       <c r="H40" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B41">
         <v>2020</v>
@@ -1839,44 +1836,44 @@
         <v>4</v>
       </c>
       <c r="D41" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F41" t="s">
         <v>6</v>
       </c>
       <c r="G41" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H41" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B42">
         <v>2018</v>
       </c>
       <c r="C42" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D42" t="s">
         <v>3</v>
       </c>
       <c r="F42" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G42" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H42" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B43">
         <v>2018</v>
@@ -1885,24 +1882,24 @@
         <v>4</v>
       </c>
       <c r="D43" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E43" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="F43" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G43" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H43" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B44">
         <v>2018</v>
@@ -1914,18 +1911,18 @@
         <v>3</v>
       </c>
       <c r="F44" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G44" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H44" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B45">
         <v>2018</v>
@@ -1940,38 +1937,38 @@
         <v>6</v>
       </c>
       <c r="G45" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H45" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B46">
         <v>2010</v>
       </c>
       <c r="C46" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D46" t="s">
         <v>3</v>
       </c>
       <c r="F46" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G46" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H46" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B47">
         <v>2018</v>
@@ -1986,15 +1983,15 @@
         <v>6</v>
       </c>
       <c r="G47" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H47" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B48">
         <v>2020</v>
@@ -2006,18 +2003,18 @@
         <v>3</v>
       </c>
       <c r="F48" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G48" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H48" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B49">
         <v>2020</v>
@@ -2032,15 +2029,15 @@
         <v>6</v>
       </c>
       <c r="G49" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H49" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B50">
         <v>2014</v>
@@ -2052,18 +2049,18 @@
         <v>3</v>
       </c>
       <c r="F50" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G50" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H50" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B51">
         <v>2018</v>
@@ -2078,15 +2075,15 @@
         <v>6</v>
       </c>
       <c r="G51" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H51" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B52">
         <v>2020</v>
@@ -2098,41 +2095,41 @@
         <v>3</v>
       </c>
       <c r="F52" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G52" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H52" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B53">
         <v>2020</v>
       </c>
       <c r="C53" t="s">
-        <v>7</v>
+        <v>159</v>
       </c>
       <c r="D53" t="s">
         <v>3</v>
       </c>
       <c r="F53" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G53" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H53" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B54">
         <v>2020</v>
@@ -2141,27 +2138,27 @@
         <v>4</v>
       </c>
       <c r="D54" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F54" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G54" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H54" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B55">
         <v>2018</v>
       </c>
       <c r="C55" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D55" t="s">
         <v>3</v>
@@ -2170,61 +2167,61 @@
         <v>6</v>
       </c>
       <c r="G55" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H55" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B56">
         <v>2016</v>
       </c>
       <c r="C56" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D56" t="s">
         <v>3</v>
       </c>
       <c r="F56" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G56" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H56" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B57">
         <v>2021</v>
       </c>
       <c r="C57" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D57" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F57" t="s">
         <v>6</v>
       </c>
       <c r="G57" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H57" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B58">
         <v>2020</v>
@@ -2233,24 +2230,24 @@
         <v>4</v>
       </c>
       <c r="D58" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E58" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="F58" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G58" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H58" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B59">
         <v>2019</v>
@@ -2259,21 +2256,21 @@
         <v>4</v>
       </c>
       <c r="D59" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F59" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G59" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H59" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B60">
         <v>2019</v>
@@ -2282,21 +2279,21 @@
         <v>4</v>
       </c>
       <c r="D60" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F60" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G60" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H60" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B61">
         <v>2020</v>
@@ -2305,21 +2302,21 @@
         <v>4</v>
       </c>
       <c r="D61" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F61" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G61" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H61" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B62">
         <v>2020</v>
@@ -2334,15 +2331,15 @@
         <v>6</v>
       </c>
       <c r="G62" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H62" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B63">
         <v>2020</v>
@@ -2354,18 +2351,18 @@
         <v>3</v>
       </c>
       <c r="F63" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G63" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H63" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B64">
         <v>2020</v>
@@ -2374,44 +2371,44 @@
         <v>4</v>
       </c>
       <c r="D64" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F64" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G64" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H64" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B65">
         <v>2020</v>
       </c>
       <c r="C65" t="s">
-        <v>7</v>
+        <v>159</v>
       </c>
       <c r="D65" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F65" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G65" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H65" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B66">
         <v>2020</v>
@@ -2420,21 +2417,21 @@
         <v>4</v>
       </c>
       <c r="D66" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F66" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G66" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H66" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B67">
         <v>2017</v>
@@ -2446,18 +2443,18 @@
         <v>3</v>
       </c>
       <c r="F67" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G67" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H67" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B68">
         <v>2020</v>
@@ -2475,12 +2472,12 @@
         <v>5</v>
       </c>
       <c r="H68" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B69">
         <v>2020</v>
@@ -2492,18 +2489,18 @@
         <v>3</v>
       </c>
       <c r="F69" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G69" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H69" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B70">
         <v>2020</v>
@@ -2518,15 +2515,15 @@
         <v>6</v>
       </c>
       <c r="G70" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H70" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B71">
         <v>2020</v>
@@ -2538,18 +2535,18 @@
         <v>3</v>
       </c>
       <c r="F71" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G71" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H71" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B72">
         <v>2019</v>
@@ -2564,15 +2561,15 @@
         <v>6</v>
       </c>
       <c r="G72" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H72" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B73">
         <v>2019</v>
@@ -2584,24 +2581,24 @@
         <v>3</v>
       </c>
       <c r="F73" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G73" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H73" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B74">
         <v>2020</v>
       </c>
       <c r="C74" t="s">
-        <v>90</v>
+        <v>159</v>
       </c>
       <c r="D74" t="s">
         <v>3</v>
@@ -2610,38 +2607,38 @@
         <v>6</v>
       </c>
       <c r="G74" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H74" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B75">
         <v>2020</v>
       </c>
       <c r="C75" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D75" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F75" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G75" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H75" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B76">
         <v>2020</v>
@@ -2650,21 +2647,21 @@
         <v>4</v>
       </c>
       <c r="D76" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F76" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G76" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H76" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B77">
         <v>2019</v>
@@ -2676,41 +2673,41 @@
         <v>3</v>
       </c>
       <c r="F77" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G77" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H77" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B78">
         <v>2016</v>
       </c>
       <c r="C78" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D78" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F78" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G78" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H78" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B79">
         <v>2019</v>
@@ -2719,24 +2716,24 @@
         <v>4</v>
       </c>
       <c r="D79" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E79" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="F79" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G79" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H79" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B80">
         <v>2019</v>
@@ -2751,15 +2748,15 @@
         <v>6</v>
       </c>
       <c r="G80" t="s">
-        <v>42</v>
+        <v>160</v>
       </c>
       <c r="H80" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B81">
         <v>2019</v>
@@ -2768,47 +2765,47 @@
         <v>4</v>
       </c>
       <c r="D81" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E81" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F81" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G81" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H81" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B82">
         <v>2020</v>
       </c>
       <c r="C82" t="s">
-        <v>90</v>
+        <v>159</v>
       </c>
       <c r="D82" t="s">
         <v>3</v>
       </c>
       <c r="F82" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G82" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H82" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B83">
         <v>2019</v>
@@ -2817,24 +2814,24 @@
         <v>4</v>
       </c>
       <c r="D83" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E83" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="F83" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G83" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H83" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B84">
         <v>2020</v>
@@ -2846,18 +2843,18 @@
         <v>3</v>
       </c>
       <c r="F84" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G84" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H84" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B85">
         <v>2019</v>
@@ -2866,24 +2863,24 @@
         <v>4</v>
       </c>
       <c r="D85" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E85" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="F85" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G85" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H85" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B86">
         <v>2018</v>
@@ -2892,24 +2889,24 @@
         <v>4</v>
       </c>
       <c r="D86" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E86" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="F86" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G86" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H86" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B87">
         <v>2018</v>
@@ -2918,24 +2915,24 @@
         <v>4</v>
       </c>
       <c r="D87" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E87" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="F87" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G87" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H87" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B88">
         <v>2018</v>
@@ -2944,44 +2941,44 @@
         <v>4</v>
       </c>
       <c r="D88" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F88" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G88" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H88" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B89">
         <v>2017</v>
       </c>
       <c r="C89" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D89" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F89" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G89" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H89" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B90">
         <v>2019</v>
@@ -2993,67 +2990,67 @@
         <v>3</v>
       </c>
       <c r="F90" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G90" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H90" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B91">
         <v>2019</v>
       </c>
       <c r="C91" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D91" t="s">
         <v>3</v>
       </c>
       <c r="F91" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G91" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H91" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B92">
         <v>2017</v>
       </c>
       <c r="C92" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D92" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E92" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="F92" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G92" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H92" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B93">
         <v>2017</v>
@@ -3065,41 +3062,41 @@
         <v>3</v>
       </c>
       <c r="F93" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G93" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H93" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B94">
         <v>2019</v>
       </c>
       <c r="C94" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D94" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F94" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G94" t="s">
-        <v>42</v>
+        <v>160</v>
       </c>
       <c r="H94" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B95">
         <v>2020</v>
@@ -3111,18 +3108,18 @@
         <v>3</v>
       </c>
       <c r="F95" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G95" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H95" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B96">
         <v>2021</v>
@@ -3134,18 +3131,18 @@
         <v>3</v>
       </c>
       <c r="F96" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G96" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H96" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B97">
         <v>2021</v>
@@ -3154,21 +3151,21 @@
         <v>4</v>
       </c>
       <c r="D97" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F97" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G97" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H97" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B98">
         <v>2021</v>
@@ -3183,15 +3180,15 @@
         <v>6</v>
       </c>
       <c r="G98" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H98" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B99">
         <v>2021</v>
@@ -3206,15 +3203,15 @@
         <v>6</v>
       </c>
       <c r="G99" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H99" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B100">
         <v>2020</v>
@@ -3229,21 +3226,21 @@
         <v>6</v>
       </c>
       <c r="G100" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H100" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B101">
         <v>2020</v>
       </c>
       <c r="C101" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D101" t="s">
         <v>3</v>
@@ -3255,12 +3252,12 @@
         <v>5</v>
       </c>
       <c r="H101" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B102">
         <v>2020</v>
@@ -3269,21 +3266,21 @@
         <v>4</v>
       </c>
       <c r="D102" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F102" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G102" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H102" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B103">
         <v>2020</v>
@@ -3292,24 +3289,24 @@
         <v>4</v>
       </c>
       <c r="D103" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E103" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F103" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G103" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H103" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B104">
         <v>2019</v>
@@ -3318,24 +3315,24 @@
         <v>4</v>
       </c>
       <c r="D104" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E104" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="F104" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G104" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H104" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B105">
         <v>2022</v>
@@ -3350,15 +3347,15 @@
         <v>6</v>
       </c>
       <c r="G105" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H105" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B106">
         <v>2017</v>
@@ -3370,44 +3367,44 @@
         <v>3</v>
       </c>
       <c r="F106" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G106" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="H106" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B107">
         <v>2016</v>
       </c>
       <c r="C107" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D107" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E107" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F107" t="s">
         <v>6</v>
       </c>
       <c r="G107" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H107" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B108">
         <v>2011</v>
@@ -3416,21 +3413,21 @@
         <v>4</v>
       </c>
       <c r="D108" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F108" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G108" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H108" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B109">
         <v>2020</v>
@@ -3439,44 +3436,44 @@
         <v>4</v>
       </c>
       <c r="D109" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F109" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G109" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H109" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B110">
         <v>2024</v>
       </c>
       <c r="C110" t="s">
-        <v>7</v>
+        <v>159</v>
       </c>
       <c r="D110" t="s">
         <v>3</v>
       </c>
       <c r="F110" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G110" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H110" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B111">
         <v>2022</v>
@@ -3485,24 +3482,24 @@
         <v>4</v>
       </c>
       <c r="D111" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E111" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F111" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G111" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="H111" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B112">
         <v>2021</v>
@@ -3514,18 +3511,18 @@
         <v>3</v>
       </c>
       <c r="F112" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G112" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H112" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B113">
         <v>2024</v>
@@ -3537,18 +3534,18 @@
         <v>3</v>
       </c>
       <c r="F113" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G113" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H113" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B114">
         <v>2024</v>
@@ -3557,19 +3554,19 @@
         <v>4</v>
       </c>
       <c r="D114" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E114" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F114" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G114" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H114" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
   </sheetData>
